--- a/data/trans_orig/P16A02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A02-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2007</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72969</t>
+          <t>72071</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107125</t>
+          <t>106653</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119523</t>
+          <t>119574</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158317</t>
+          <t>158439</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>201796</t>
+          <t>202065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>255593</t>
+          <t>254656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>585869</t>
+          <t>586341</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>620025</t>
+          <t>620923</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>530034</t>
+          <t>529912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>568828</t>
+          <t>568777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1125752</t>
+          <t>1126689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1179549</t>
+          <t>1179280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106099</t>
+          <t>108616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150230</t>
+          <t>150567</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186327</t>
+          <t>187644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>238031</t>
+          <t>238122</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>308358</t>
+          <t>309063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>374385</t>
+          <t>377359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>811570</t>
+          <t>811233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>855701</t>
+          <t>853184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>730362</t>
+          <t>730271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>782066</t>
+          <t>780749</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1555808</t>
+          <t>1552834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1621835</t>
+          <t>1621130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68165</t>
+          <t>68279</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103809</t>
+          <t>101893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154732</t>
+          <t>155850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202347</t>
+          <t>203448</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231658</t>
+          <t>232458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>289182</t>
+          <t>288916</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>574700</t>
+          <t>576616</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>610344</t>
+          <t>610230</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>481494</t>
+          <t>480393</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>529109</t>
+          <t>527991</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1073168</t>
+          <t>1073434</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1130692</t>
+          <t>1129892</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136809</t>
+          <t>132523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179303</t>
+          <t>174944</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>250231</t>
+          <t>248449</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>308547</t>
+          <t>304407</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>397427</t>
+          <t>398851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>467391</t>
+          <t>468008</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>762919</t>
+          <t>767278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>805413</t>
+          <t>809699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>730065</t>
+          <t>734205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>788381</t>
+          <t>790163</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1513443</t>
+          <t>1512826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1583407</t>
+          <t>1581983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>419332</t>
+          <t>419788</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>499643</t>
+          <t>494030</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>760960</t>
+          <t>758119</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>859025</t>
+          <t>857376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1199751</t>
+          <t>1197256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1327515</t>
+          <t>1327501</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2775882</t>
+          <t>2781495</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2856193</t>
+          <t>2855737</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2520172</t>
+          <t>2521821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2618237</t>
+          <t>2621078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5327207</t>
+          <t>5327221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5454971</t>
+          <t>5457466</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2012</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103711</t>
+          <t>100544</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>143465</t>
+          <t>142344</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>206355</t>
+          <t>207837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257344</t>
+          <t>257458</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>321396</t>
+          <t>317908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>387895</t>
+          <t>383367</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>557299</t>
+          <t>558420</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>597053</t>
+          <t>600220</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>438663</t>
+          <t>438549</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>489652</t>
+          <t>488170</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1008875</t>
+          <t>1013403</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1075374</t>
+          <t>1078862</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167997</t>
+          <t>168998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220846</t>
+          <t>222326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>296273</t>
+          <t>295545</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>357587</t>
+          <t>356463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>477040</t>
+          <t>480984</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>561102</t>
+          <t>558325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>797101</t>
+          <t>795621</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>849950</t>
+          <t>848949</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>671371</t>
+          <t>672495</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>732685</t>
+          <t>733413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1485803</t>
+          <t>1488580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1569865</t>
+          <t>1565921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,5%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103579</t>
+          <t>103961</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147746</t>
+          <t>146128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>219407</t>
+          <t>220543</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>275248</t>
+          <t>275919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>336332</t>
+          <t>339935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>404928</t>
+          <t>407976</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608792</t>
+          <t>610410</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652959</t>
+          <t>652577</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>501035</t>
+          <t>500364</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>556876</t>
+          <t>555740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1127893</t>
+          <t>1124845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1196489</t>
+          <t>1192886</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148910</t>
+          <t>147926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196320</t>
+          <t>196355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>354010</t>
+          <t>354101</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>418361</t>
+          <t>419510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>517194</t>
+          <t>516632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>601306</t>
+          <t>601453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>749610</t>
+          <t>749575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>797020</t>
+          <t>798004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>631385</t>
+          <t>630236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>695736</t>
+          <t>695645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394371</t>
+          <t>1394224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1478483</t>
+          <t>1479045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,11%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>566113</t>
+          <t>564915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>663418</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1129279</t>
+          <t>1134909</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1248204</t>
+          <t>1247662</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1728497</t>
+          <t>1729485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1880953</t>
+          <t>1884212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2762790</t>
+          <t>2757761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2855066</t>
+          <t>2856264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2302791</t>
+          <t>2303333</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2421716</t>
+          <t>2416086</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5091221</t>
+          <t>5087962</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5243677</t>
+          <t>5242689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2016</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109342</t>
+          <t>108357</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>149541</t>
+          <t>147076</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>195638</t>
+          <t>196163</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>244882</t>
+          <t>245648</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>316909</t>
+          <t>317938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>381918</t>
+          <t>382338</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>525259</t>
+          <t>527724</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>565458</t>
+          <t>566443</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427957</t>
+          <t>427191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>477201</t>
+          <t>476676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>965721</t>
+          <t>965301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1030730</t>
+          <t>1029701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,41%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>176894</t>
+          <t>175860</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>231388</t>
+          <t>229884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>268869</t>
+          <t>269249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>329748</t>
+          <t>330027</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>457316</t>
+          <t>456423</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>540675</t>
+          <t>540047</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>791043</t>
+          <t>792547</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>845537</t>
+          <t>846571</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>713165</t>
+          <t>712886</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>774044</t>
+          <t>773664</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1524669</t>
+          <t>1525297</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1608028</t>
+          <t>1608921</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,9%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92493</t>
+          <t>93937</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132463</t>
+          <t>133224</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>197883</t>
+          <t>197266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249685</t>
+          <t>249905</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>304964</t>
+          <t>301566</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>369734</t>
+          <t>369353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627089</t>
+          <t>626328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667059</t>
+          <t>665615</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>535326</t>
+          <t>535106</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>587128</t>
+          <t>587745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1174829</t>
+          <t>1175210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1239599</t>
+          <t>1242997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172285</t>
+          <t>171815</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>222366</t>
+          <t>220659</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>333548</t>
+          <t>328822</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>396643</t>
+          <t>395406</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>517976</t>
+          <t>518635</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>600520</t>
+          <t>600673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>715201</t>
+          <t>716908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>765282</t>
+          <t>765752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>647136</t>
+          <t>648373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>710231</t>
+          <t>714957</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1380826</t>
+          <t>1380673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1463370</t>
+          <t>1462711</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>599790</t>
+          <t>596489</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>685922</t>
+          <t>685443</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1043727</t>
+          <t>1045830</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1156043</t>
+          <t>1162104</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1666980</t>
+          <t>1673737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1821371</t>
+          <t>1828832</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2708428</t>
+          <t>2708907</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2794560</t>
+          <t>2797861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2388499</t>
+          <t>2382438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2500815</t>
+          <t>2498712</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5117521</t>
+          <t>5110060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5271912</t>
+          <t>5265155</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2023</t>
+          <t>Población según si ha consumido medicinas para el dolor/bajar la fiebre en las dos últimas semanas en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149312</t>
+          <t>151015</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>197127</t>
+          <t>198564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>252380</t>
+          <t>249625</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>289921</t>
+          <t>289549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>417579</t>
+          <t>414140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>480832</t>
+          <t>477707</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>438314</t>
+          <t>436877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486129</t>
+          <t>484426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>385831</t>
+          <t>386203</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423372</t>
+          <t>426127</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>830362</t>
+          <t>833487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>893615</t>
+          <t>897054</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,42%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112368</t>
+          <t>98848</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>274155</t>
+          <t>269880</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>351599</t>
+          <t>353143</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>401713</t>
+          <t>402895</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>393374</t>
+          <t>394075</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>672074</t>
+          <t>671747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>918709</t>
+          <t>922984</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1080496</t>
+          <t>1094016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556393</t>
+          <t>555211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>606507</t>
+          <t>604963</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1478897</t>
+          <t>1479224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1757597</t>
+          <t>1756896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138391</t>
+          <t>137649</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187824</t>
+          <t>190149</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>324103</t>
+          <t>323119</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>681141</t>
+          <t>700785</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>471410</t>
+          <t>471685</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>971931</t>
+          <t>958835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>58,54%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516856</t>
+          <t>514531</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>566289</t>
+          <t>567031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>252225</t>
+          <t>232581</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>609263</t>
+          <t>610247</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>666115</t>
+          <t>679211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1166636</t>
+          <t>1166361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>207007</t>
+          <t>207715</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262776</t>
+          <t>264792</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>323921</t>
+          <t>340369</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>457851</t>
+          <t>458847</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>576072</t>
+          <t>577258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>699230</t>
+          <t>695684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>664055</t>
+          <t>662039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>719824</t>
+          <t>719116</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>633523</t>
+          <t>632527</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>767453</t>
+          <t>751005</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1318975</t>
+          <t>1322521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1442133</t>
+          <t>1440947</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>602104</t>
+          <t>606557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>855818</t>
+          <t>862316</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1387080</t>
+          <t>1376601</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1944977</t>
+          <t>1886597</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2074461</t>
+          <t>2089193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2778298</t>
+          <t>2761143</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2603999</t>
+          <t>2597501</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2857713</t>
+          <t>2853260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1713621</t>
+          <t>1772001</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2271518</t>
+          <t>2281997</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4340117</t>
+          <t>4357272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5043954</t>
+          <t>5029222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A02-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72071</t>
+          <t>72171</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106653</t>
+          <t>108224</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119574</t>
+          <t>120441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158439</t>
+          <t>161039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>202065</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254656</t>
+          <t>255783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>586341</t>
+          <t>584770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>620923</t>
+          <t>620823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>529912</t>
+          <t>527312</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>568777</t>
+          <t>567910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1126689</t>
+          <t>1125562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1179280</t>
+          <t>1179488</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108616</t>
+          <t>107505</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150567</t>
+          <t>150989</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187644</t>
+          <t>187672</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>238122</t>
+          <t>244604</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>309063</t>
+          <t>309293</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>377359</t>
+          <t>375926</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>811233</t>
+          <t>810811</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>853184</t>
+          <t>854295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>730271</t>
+          <t>723789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>780749</t>
+          <t>780721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1552834</t>
+          <t>1554267</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1621130</t>
+          <t>1620900</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68279</t>
+          <t>66905</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101893</t>
+          <t>101385</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155850</t>
+          <t>154697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>203448</t>
+          <t>200383</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>232458</t>
+          <t>233364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288916</t>
+          <t>292131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>576616</t>
+          <t>577124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>610230</t>
+          <t>611604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>480393</t>
+          <t>483458</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>527991</t>
+          <t>529144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1073434</t>
+          <t>1070219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1129892</t>
+          <t>1128986</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,87%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132523</t>
+          <t>135917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174944</t>
+          <t>178627</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>248449</t>
+          <t>248020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>304407</t>
+          <t>306453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>398851</t>
+          <t>397790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>468008</t>
+          <t>470788</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>767278</t>
+          <t>763595</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>809699</t>
+          <t>806305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>734205</t>
+          <t>732159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>790163</t>
+          <t>790592</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1512826</t>
+          <t>1510046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1581983</t>
+          <t>1583044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,92%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>419788</t>
+          <t>418796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>494030</t>
+          <t>496828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>758119</t>
+          <t>752583</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>857376</t>
+          <t>853098</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1197256</t>
+          <t>1194525</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1327501</t>
+          <t>1326086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2781495</t>
+          <t>2778697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2855737</t>
+          <t>2856729</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2521821</t>
+          <t>2526099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2621078</t>
+          <t>2626614</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5327221</t>
+          <t>5328636</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5457466</t>
+          <t>5460197</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100544</t>
+          <t>102457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142344</t>
+          <t>142508</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>207837</t>
+          <t>205368</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257458</t>
+          <t>256563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>317908</t>
+          <t>320844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>383367</t>
+          <t>388210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>558420</t>
+          <t>558256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>600220</t>
+          <t>598307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>438549</t>
+          <t>439444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>488170</t>
+          <t>490639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1013403</t>
+          <t>1008560</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1078862</t>
+          <t>1075926</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168998</t>
+          <t>170861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>222326</t>
+          <t>223226</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>295545</t>
+          <t>294032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>356463</t>
+          <t>357135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>480984</t>
+          <t>481836</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>558325</t>
+          <t>556651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>795621</t>
+          <t>794721</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>848949</t>
+          <t>847086</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>672495</t>
+          <t>671823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>733413</t>
+          <t>734926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1488580</t>
+          <t>1490254</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1565921</t>
+          <t>1565069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103961</t>
+          <t>103688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146128</t>
+          <t>146174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>220543</t>
+          <t>220691</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>275919</t>
+          <t>273770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>339935</t>
+          <t>337754</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>407976</t>
+          <t>409165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610410</t>
+          <t>610364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>652577</t>
+          <t>652850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>500364</t>
+          <t>502513</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>555740</t>
+          <t>555592</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1124845</t>
+          <t>1123656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1192886</t>
+          <t>1195067</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>147926</t>
+          <t>147418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>196355</t>
+          <t>198898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>354101</t>
+          <t>353236</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>419510</t>
+          <t>417649</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>516632</t>
+          <t>518052</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>601453</t>
+          <t>601011</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>749575</t>
+          <t>747032</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>798004</t>
+          <t>798512</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>630236</t>
+          <t>632097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>695645</t>
+          <t>696510</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394224</t>
+          <t>1394666</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1479045</t>
+          <t>1477625</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>564915</t>
+          <t>561679</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>663418</t>
+          <t>661042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1134909</t>
+          <t>1129220</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1247662</t>
+          <t>1246793</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1729485</t>
+          <t>1725197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1884212</t>
+          <t>1880104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2757761</t>
+          <t>2760137</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2856264</t>
+          <t>2859500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2303333</t>
+          <t>2304202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2416086</t>
+          <t>2421775</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5087962</t>
+          <t>5092070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5242689</t>
+          <t>5246977</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108357</t>
+          <t>109186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147076</t>
+          <t>150804</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>196163</t>
+          <t>196561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>245648</t>
+          <t>247095</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>317938</t>
+          <t>316447</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>382338</t>
+          <t>381722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>527724</t>
+          <t>523996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>566443</t>
+          <t>565614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427191</t>
+          <t>425744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>476676</t>
+          <t>476278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>965301</t>
+          <t>965917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1029701</t>
+          <t>1031192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,52%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175860</t>
+          <t>174370</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>229884</t>
+          <t>226883</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>269249</t>
+          <t>268306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>330027</t>
+          <t>329072</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>456423</t>
+          <t>458307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>540047</t>
+          <t>541408</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>792547</t>
+          <t>795548</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>846571</t>
+          <t>848061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>712886</t>
+          <t>713841</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>773664</t>
+          <t>774607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1525297</t>
+          <t>1523936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1608921</t>
+          <t>1607037</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,81%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93937</t>
+          <t>95025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133224</t>
+          <t>133164</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>197266</t>
+          <t>198638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249905</t>
+          <t>247096</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>301566</t>
+          <t>298666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>369353</t>
+          <t>365841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626328</t>
+          <t>626388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665615</t>
+          <t>664527</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>535106</t>
+          <t>537915</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>587745</t>
+          <t>586373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1175210</t>
+          <t>1178722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1242997</t>
+          <t>1245897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171815</t>
+          <t>173790</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>220659</t>
+          <t>224173</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>328822</t>
+          <t>329879</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>395406</t>
+          <t>392817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>518635</t>
+          <t>517297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>600673</t>
+          <t>601267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>716908</t>
+          <t>713394</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>765752</t>
+          <t>763777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>648373</t>
+          <t>650962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>714957</t>
+          <t>713900</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1380673</t>
+          <t>1380079</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1462711</t>
+          <t>1464049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,89%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>596489</t>
+          <t>595150</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>685443</t>
+          <t>688038</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1045830</t>
+          <t>1050441</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1162104</t>
+          <t>1161428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1673737</t>
+          <t>1673551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1828832</t>
+          <t>1815264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2708907</t>
+          <t>2706312</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2797861</t>
+          <t>2799200</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2382438</t>
+          <t>2383114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2498712</t>
+          <t>2494101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5110060</t>
+          <t>5123628</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5265155</t>
+          <t>5265341</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>173659</t>
+          <t>190046</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>151015</t>
+          <t>163985</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198564</t>
+          <t>215009</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>270921</t>
+          <t>290148</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>249625</t>
+          <t>269079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>289549</t>
+          <t>311613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>444581</t>
+          <t>480194</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>414140</t>
+          <t>448249</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>477707</t>
+          <t>517786</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>461782</t>
+          <t>500664</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>436877</t>
+          <t>475701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484426</t>
+          <t>526725</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>404831</t>
+          <t>442965</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>386203</t>
+          <t>421500</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>426127</t>
+          <t>464034</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>866613</t>
+          <t>943629</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>833487</t>
+          <t>906037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>897054</t>
+          <t>975574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,52%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>207499</t>
+          <t>224970</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98848</t>
+          <t>195134</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269880</t>
+          <t>253561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>376901</t>
+          <t>417875</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>353143</t>
+          <t>388139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>402895</t>
+          <t>444246</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>584400</t>
+          <t>642845</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>394075</t>
+          <t>603459</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>671747</t>
+          <t>685281</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>985365</t>
+          <t>823947</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>922984</t>
+          <t>795356</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1094016</t>
+          <t>853783</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>581205</t>
+          <t>652963</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555211</t>
+          <t>626592</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>604963</t>
+          <t>682699</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1566571</t>
+          <t>1476910</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1479224</t>
+          <t>1434474</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1756896</t>
+          <t>1516296</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>162113</t>
+          <t>180676</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137649</t>
+          <t>155844</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190149</t>
+          <t>208413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>467984</t>
+          <t>297675</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>323119</t>
+          <t>271348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>700785</t>
+          <t>321373</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>630097</t>
+          <t>478352</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>471685</t>
+          <t>441807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>958835</t>
+          <t>513891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>542567</t>
+          <t>622397</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514531</t>
+          <t>594660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>567031</t>
+          <t>647229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>465382</t>
+          <t>514584</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232581</t>
+          <t>490886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>610247</t>
+          <t>540911</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1007949</t>
+          <t>1136980</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>679211</t>
+          <t>1101441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1166361</t>
+          <t>1173525</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>72,65%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>233522</t>
+          <t>243634</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>207715</t>
+          <t>219212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>264792</t>
+          <t>271951</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>418576</t>
+          <t>448810</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>340369</t>
+          <t>421421</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>458847</t>
+          <t>477048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>652098</t>
+          <t>692444</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>577258</t>
+          <t>651809</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>695684</t>
+          <t>734875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>693309</t>
+          <t>746428</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>662039</t>
+          <t>718111</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>719116</t>
+          <t>770850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>672798</t>
+          <t>668221</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>632527</t>
+          <t>639983</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>751005</t>
+          <t>695610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1366107</t>
+          <t>1414649</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1322521</t>
+          <t>1372218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1440947</t>
+          <t>1455284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>776794</t>
+          <t>839327</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>606557</t>
+          <t>786469</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>862316</t>
+          <t>898424</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1534383</t>
+          <t>1454508</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1376601</t>
+          <t>1401329</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1886597</t>
+          <t>1502432</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2311177</t>
+          <t>2293836</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2089193</t>
+          <t>2225276</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2761143</t>
+          <t>2370307</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2683023</t>
+          <t>2693435</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2597501</t>
+          <t>2634338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2853260</t>
+          <t>2746293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2124215</t>
+          <t>2278733</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1772001</t>
+          <t>2230809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2281997</t>
+          <t>2331912</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4807238</t>
+          <t>4972167</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4357272</t>
+          <t>4895696</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5029222</t>
+          <t>5040727</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658598</t>
+          <t>3733241</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7118415</t>
+          <t>7266003</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
